--- a/data/predictions/Chris.xlsx
+++ b/data/predictions/Chris.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb8ff3dc0463a38e/Documents/Personal Projects/World Cup/data/predictions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="8_{1345D99A-D3F2-4019-AE5D-47DDA7725B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A88F1E10-84C7-4662-8421-A795FCB0B9B9}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{1345D99A-D3F2-4019-AE5D-47DDA7725B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{684D56F9-89A4-4E8E-AB4B-2836701BF89E}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -540,7 +540,7 @@
   <dimension ref="A1:G1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>

--- a/data/predictions/Chris.xlsx
+++ b/data/predictions/Chris.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb8ff3dc0463a38e/Documents/Personal Projects/World Cup/data/predictions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{1345D99A-D3F2-4019-AE5D-47DDA7725B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{684D56F9-89A4-4E8E-AB4B-2836701BF89E}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="8_{1345D99A-D3F2-4019-AE5D-47DDA7725B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{656E9039-C924-4CA1-9261-0C0B5C7EA5B8}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1756,11 +1756,15 @@
       <c r="C53" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D53" s="5"/>
+      <c r="D53" s="5">
+        <v>1</v>
+      </c>
       <c r="E53" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F53" s="5"/>
+      <c r="F53" s="5">
+        <v>4</v>
+      </c>
       <c r="G53" s="4" t="s">
         <v>21</v>
       </c>
@@ -1775,11 +1779,15 @@
       <c r="C54" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D54" s="5"/>
+      <c r="D54" s="5">
+        <v>0</v>
+      </c>
       <c r="E54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F54" s="5"/>
+      <c r="F54" s="5">
+        <v>2</v>
+      </c>
       <c r="G54" s="4" t="s">
         <v>10</v>
       </c>
@@ -1794,11 +1802,15 @@
       <c r="C55" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D55" s="5"/>
+      <c r="D55" s="5">
+        <v>1</v>
+      </c>
       <c r="E55" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F55" s="5"/>
+      <c r="F55" s="5">
+        <v>3</v>
+      </c>
       <c r="G55" s="4" t="s">
         <v>8</v>
       </c>
@@ -1813,11 +1825,15 @@
       <c r="C56" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D56" s="5"/>
+      <c r="D56" s="5">
+        <v>1</v>
+      </c>
       <c r="E56" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F56" s="5"/>
+      <c r="F56" s="5">
+        <v>2</v>
+      </c>
       <c r="G56" s="4" t="s">
         <v>33</v>
       </c>
@@ -1832,11 +1848,15 @@
       <c r="C57" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D57" s="5"/>
+      <c r="D57" s="5">
+        <v>1</v>
+      </c>
       <c r="E57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F57" s="5"/>
+      <c r="F57" s="5">
+        <v>4</v>
+      </c>
       <c r="G57" s="4" t="s">
         <v>28</v>
       </c>
@@ -1851,11 +1871,15 @@
       <c r="C58" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D58" s="5"/>
+      <c r="D58" s="5">
+        <v>0</v>
+      </c>
       <c r="E58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F58" s="5"/>
+      <c r="F58" s="5">
+        <v>3</v>
+      </c>
       <c r="G58" s="4" t="s">
         <v>31</v>
       </c>
@@ -1870,11 +1894,15 @@
       <c r="C59" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D59" s="5"/>
+      <c r="D59" s="5">
+        <v>2</v>
+      </c>
       <c r="E59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F59" s="5"/>
+      <c r="F59" s="5">
+        <v>2</v>
+      </c>
       <c r="G59" s="4" t="s">
         <v>35</v>
       </c>
@@ -1889,11 +1917,15 @@
       <c r="C60" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="5"/>
+      <c r="D60" s="5">
+        <v>0</v>
+      </c>
       <c r="E60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F60" s="5"/>
+      <c r="F60" s="5">
+        <v>0</v>
+      </c>
       <c r="G60" s="4" t="s">
         <v>25</v>
       </c>
@@ -1908,11 +1940,15 @@
       <c r="C61" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D61" s="5"/>
+      <c r="D61" s="5">
+        <v>1</v>
+      </c>
       <c r="E61" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F61" s="5"/>
+      <c r="F61" s="5">
+        <v>2</v>
+      </c>
       <c r="G61" s="4" t="s">
         <v>16</v>
       </c>
@@ -1927,11 +1963,15 @@
       <c r="C62" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D62" s="5"/>
+      <c r="D62" s="5">
+        <v>1</v>
+      </c>
       <c r="E62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F62" s="5"/>
+      <c r="F62" s="5">
+        <v>3</v>
+      </c>
       <c r="G62" s="4" t="s">
         <v>48</v>
       </c>
@@ -1946,11 +1986,15 @@
       <c r="C63" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D63" s="5"/>
+      <c r="D63" s="5">
+        <v>2</v>
+      </c>
       <c r="E63" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F63" s="5"/>
+      <c r="F63" s="5">
+        <v>0</v>
+      </c>
       <c r="G63" s="4" t="s">
         <v>50</v>
       </c>
@@ -1965,11 +2009,15 @@
       <c r="C64" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D64" s="5"/>
+      <c r="D64" s="5">
+        <v>0</v>
+      </c>
       <c r="E64" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F64" s="5"/>
+      <c r="F64" s="5">
+        <v>4</v>
+      </c>
       <c r="G64" s="4" t="s">
         <v>43</v>
       </c>
@@ -1984,11 +2032,15 @@
       <c r="C65" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D65" s="5"/>
+      <c r="D65" s="5">
+        <v>2</v>
+      </c>
       <c r="E65" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F65" s="5"/>
+      <c r="F65" s="5">
+        <v>4</v>
+      </c>
       <c r="G65" s="4" t="s">
         <v>38</v>
       </c>
@@ -2003,11 +2055,15 @@
       <c r="C66" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D66" s="5"/>
+      <c r="D66" s="5">
+        <v>0</v>
+      </c>
       <c r="E66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F66" s="5"/>
+      <c r="F66" s="5">
+        <v>0</v>
+      </c>
       <c r="G66" s="4" t="s">
         <v>45</v>
       </c>
@@ -2022,11 +2078,15 @@
       <c r="C67" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D67" s="5"/>
+      <c r="D67" s="5">
+        <v>0</v>
+      </c>
       <c r="E67" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F67" s="5"/>
+      <c r="F67" s="5">
+        <v>3</v>
+      </c>
       <c r="G67" s="4" t="s">
         <v>41</v>
       </c>
@@ -2041,11 +2101,15 @@
       <c r="C68" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D68" s="5"/>
+      <c r="D68" s="5">
+        <v>2</v>
+      </c>
       <c r="E68" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F68" s="5"/>
+      <c r="F68" s="5">
+        <v>0</v>
+      </c>
       <c r="G68" s="4" t="s">
         <v>63</v>
       </c>
@@ -2060,11 +2124,15 @@
       <c r="C69" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D69" s="5"/>
+      <c r="D69" s="5">
+        <v>1</v>
+      </c>
       <c r="E69" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F69" s="5"/>
+      <c r="F69" s="5">
+        <v>3</v>
+      </c>
       <c r="G69" s="4" t="s">
         <v>61</v>
       </c>
@@ -2079,11 +2147,15 @@
       <c r="C70" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D70" s="5"/>
+      <c r="D70" s="5">
+        <v>0</v>
+      </c>
       <c r="E70" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F70" s="5"/>
+      <c r="F70" s="5">
+        <v>3</v>
+      </c>
       <c r="G70" s="4" t="s">
         <v>58</v>
       </c>
@@ -2098,11 +2170,15 @@
       <c r="C71" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D71" s="5"/>
+      <c r="D71" s="5">
+        <v>1</v>
+      </c>
       <c r="E71" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F71" s="5"/>
+      <c r="F71" s="5">
+        <v>2</v>
+      </c>
       <c r="G71" s="4" t="s">
         <v>65</v>
       </c>
@@ -2117,11 +2193,15 @@
       <c r="C72" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D72" s="5"/>
+      <c r="D72" s="5">
+        <v>0</v>
+      </c>
       <c r="E72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F72" s="5"/>
+      <c r="F72" s="5">
+        <v>2</v>
+      </c>
       <c r="G72" s="4" t="s">
         <v>55</v>
       </c>
@@ -2136,11 +2216,15 @@
       <c r="C73" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D73" s="5"/>
+      <c r="D73" s="5">
+        <v>0</v>
+      </c>
       <c r="E73" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F73" s="5"/>
+      <c r="F73" s="5">
+        <v>4</v>
+      </c>
       <c r="G73" s="4" t="s">
         <v>53</v>
       </c>
